--- a/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="309">
   <si>
     <t xml:space="preserve">Budsjettering og budsjettkontroll: oppgaver til kapittel 9</t>
   </si>
@@ -187,7 +187,13 @@
     <t xml:space="preserve">Gule celler fyller du inn. Grønne regnes ut av arket. Sjekken til høyre forteller om svaret stemmer, og hva du bør se på hvis ikke.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1B: Fjell Elektro: startbudsjettet for det første driftsåret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nei</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS er den lille bedriften som likner den dere etablerer i prosjektet «Etablering av El-bedrift»: to montører og én eier som er faglig ansvarlig og jobber halve tiden ute. Banken vil se et resultatbudsjett for det første driftsåret før den gir lån. Forutsetningene står i tabellen. Du setter opp budsjettet linje for linje og sier hva som er mest usikkert.</t>
@@ -282,9 +288,18 @@
     <t xml:space="preserve">h) Hvilken forutsetning er mest usikker, og hva gjør dere hvis den slår feil? Regn gjerne: hva skjer med driftsresultatet hvis hver montør fakturerer 200 timer mindre?</t>
   </si>
   <si>
+    <t xml:space="preserve">Bare resultatbudsjettet</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 1C: Hvor hører posten hjemme: resultatbudsjettet, likviditetsbudsjettet eller begge?</t>
   </si>
   <si>
+    <t xml:space="preserve">Bare likviditetsbudsjettet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Begge</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sara, lærlingen hos Nordlys, har sett budsjettet og spør hvorfor avdraget på lånet ikke står der, når det er den største regningen i mars. Kari ber deg sortere ti poster fra Nordlys: hører de hjemme i resultatbudsjettet, i likviditetsbudsjettet, eller i begge? Så tre små regnestykker, og en forklaring til Sara.</t>
   </si>
   <si>
@@ -342,7 +357,16 @@
     <t xml:space="preserve">d) Forklar til Sara, lærlingen, hvorfor avdraget på banklånet ikke står i resultatbudsjettet, mens renten gjør det. To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Det blir lavere, fordi inntektene kommer senere</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2A: Nordlys, første kvartal 2027: har vi penger til lønn den 15.?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det endres ikke med en krone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Det blir høyere, fordi kundene betaler renter</t>
   </si>
   <si>
     <t xml:space="preserve">Budsjettet for 2027 viser 1 770 000 kr i driftsresultat. Likevel ringer regnskapsføreren: 1. januar står det 982 650 kr på driftskontoen, Polarlys skal ha 2 100 000 for materiellet fra desember, og kundene skylder 4 200 000, men de betaler når de betaler. Kari vil se pengene måned for måned. Januar er regnet ferdig; du regner februar og mars, og så hva som skjer hvis kundene betaler senere.</t>
@@ -476,7 +500,16 @@
     <t xml:space="preserve">e) Kari skal i banken. Hva foreslår du at Nordlys gjør først, og hvorfor kommer større kassekreditt sist? Bruk minst to av lærebokas tiltak (fakturere tidlig, e-faktura, kortere kredittid, purre tidlig, forskudd på store jobber, lengre leverandørkreditt).</t>
   </si>
   <si>
+    <t xml:space="preserve">Fordi de er inntekter i oppstartsåret</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2B: Fjell Elektro: likviditeten i oppstartsmånedene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fordi likviditetsbudsjettet følger pengene, og resultatbudsjettet følger inntekter og kostnader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fordi de er fradragsberettiget</t>
   </si>
   <si>
     <t xml:space="preserve">Fjell Elektro AS (samme bedrift som i 1B) starter 1. januar med tom konto. Aksjekapital og banklån kommer inn i januar; kundene betaler etter 30 dager. Dette er startbudsjettet banken spør etter i «Etablering av El-bedrift»: holder pengene til kundene begynner å betale? Fyll inn innbetalingene og regn saldoen måned for måned.</t>
@@ -571,7 +604,16 @@
     <t xml:space="preserve">e) Merverdiavgift som forfaller 10. april: utgående avgift på salget i januar og februar, minus inngående avgift på utstyr og materiell</t>
   </si>
   <si>
+    <t xml:space="preserve">Lønnskostnaden, som gikk opp 37 500</t>
+  </si>
+  <si>
     <t xml:space="preserve">Oppgave 2C: Nordlys, første kvartal 2027: budsjett mot regnskap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekostnaden: 96 000 av avviket forklares ikke av at salget økte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avskrivningene</t>
   </si>
   <si>
     <t xml:space="preserve">Første kvartal er over. Kari setter regnskapet ved siden av budsjettet for kvartalet. Salget ble bedre enn planlagt, men driftsresultatet ble dårligere. Hun skal møte Ida (kalkulatør og innkjøp) på mandag og vil vite hva hun skal spørre om. Regn avvikene med riktig fortegn, så andelen av salget, og finn stedet Kari skal lete.</t>
@@ -1100,7 +1142,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1195,6 +1237,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2082,7 +2128,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G47"/>
+  <dimension ref="B1:Z47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2090,17 +2136,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>52</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2111,6 +2166,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2121,16 +2179,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -2141,52 +2205,75 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="Z9" s="24" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>3500</v>
       </c>
+      <c r="Z10" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C11" s="12" t="n">
         <v>890</v>
       </c>
+      <c r="Z11" s="24" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" s="12" t="n">
         <v>1400000</v>
       </c>
+      <c r="Z12" s="24" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>560000</v>
@@ -2194,7 +2281,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>700000</v>
@@ -2202,15 +2289,15 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>300000</v>
@@ -2218,7 +2305,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>519000</v>
@@ -2226,7 +2313,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>500000</v>
@@ -2234,7 +2321,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>300000</v>
@@ -2242,7 +2329,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>400</v>
@@ -2260,7 +2347,7 @@
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2270,7 +2357,7 @@
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="18" t="s">
@@ -2283,7 +2370,7 @@
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="18" t="s">
@@ -2296,7 +2383,7 @@
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="18" t="s">
@@ -2309,7 +2396,7 @@
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="18" t="s">
@@ -2322,7 +2409,7 @@
     </row>
     <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C29" s="13"/>
       <c r="D29" s="18" t="s">
@@ -2335,7 +2422,7 @@
     </row>
     <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C30" s="13"/>
       <c r="D30" s="18" t="s">
@@ -2348,7 +2435,7 @@
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="16" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" s="22"/>
       <c r="G32" s="19" t="str">
@@ -2358,7 +2445,7 @@
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C33" s="22"/>
       <c r="G33" s="19" t="str">
@@ -2368,7 +2455,7 @@
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C34" s="22"/>
       <c r="G34" s="19" t="str">
@@ -2378,7 +2465,7 @@
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C35" s="22"/>
       <c r="G35" s="19" t="str">
@@ -2388,7 +2475,7 @@
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" s="22"/>
       <c r="G36" s="19" t="str">
@@ -2398,7 +2485,7 @@
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C37" s="22"/>
       <c r="G37" s="19" t="str">
@@ -2408,7 +2495,7 @@
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -2592,27 +2679,27 @@
   </conditionalFormatting>
   <dataValidations count="7">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$1:$Z$2</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C33" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$3:$Z$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$5:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C35" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$7:$Z$8</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C36" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$9:$Z$10</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C37" type="list">
-      <formula1>"Ja,Nei"</formula1>
+      <formula1>$Z$11:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C44" type="list">
@@ -2635,7 +2722,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="B1:Z35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2643,17 +2730,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -2664,6 +2760,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -2674,16 +2773,22 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
+      <c r="Z4" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
+      <c r="Z5" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
@@ -2694,150 +2799,205 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="Z6" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
+      <c r="Z7" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z8" s="0" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="Z9" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="16" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C10" s="22"/>
       <c r="G10" s="19" t="str">
         <f aca="false">IF(C10="","Velg i nedtrekksmenyen.",IF(C10="Bare resultatbudsjettet","Riktig. Kostnad uten utbetaling. Pengene gikk ut da bilene ble kjøpt.","Ikke riktig. Kostnad uten utbetaling. Pengene gikk ut da bilene ble kjøpt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z10" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C11" s="22"/>
       <c r="G11" s="19" t="str">
         <f aca="false">IF(C11="","Velg i nedtrekksmenyen.",IF(C11="Bare likviditetsbudsjettet","Riktig. Utbetalingen skjer i mars. I resultatbudsjettet står bare avskrivningen, 10 000 per måned.","Ikke riktig. Utbetalingen skjer i mars. I resultatbudsjettet står bare avskrivningen, 10 000 per måned."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z11" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="16" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C12" s="22"/>
       <c r="G12" s="19" t="str">
         <f aca="false">IF(C12="","Velg i nedtrekksmenyen.",IF(C12="Bare likviditetsbudsjettet","Riktig. Nedbetaling av gjeld er ikke en kostnad.","Ikke riktig. Nedbetaling av gjeld er ikke en kostnad."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z12" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C13" s="22"/>
       <c r="G13" s="19" t="str">
         <f aca="false">IF(C13="","Velg i nedtrekksmenyen.",IF(C13="Begge","Riktig. Renten er en kostnad i resultatbudsjettet og en utbetaling når den forfaller.","Ikke riktig. Renten er en kostnad i resultatbudsjettet og en utbetaling når den forfaller."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z13" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="16" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C14" s="22"/>
       <c r="G14" s="19" t="str">
         <f aca="false">IF(C14="","Velg i nedtrekksmenyen.",IF(C14="Bare likviditetsbudsjettet","Riktig. Statens penger. Resultatbudsjettet settes opp uten merverdiavgift.","Ikke riktig. Statens penger. Resultatbudsjettet settes opp uten merverdiavgift."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z14" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C15" s="22"/>
       <c r="G15" s="19" t="str">
         <f aca="false">IF(C15="","Velg i nedtrekksmenyen.",IF(C15="Bare likviditetsbudsjettet","Riktig. Kostnaden ble tatt i 2026, da de ble tjent opp. I 2027 er det bare en utbetaling.","Ikke riktig. Kostnaden ble tatt i 2026, da de ble tjent opp. I 2027 er det bare en utbetaling."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z15" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C16" s="22"/>
       <c r="G16" s="19" t="str">
         <f aca="false">IF(C16="","Velg i nedtrekksmenyen.",IF(C16="Begge","Riktig. Kostnad i mars, og utbetaling når lønna betales.","Ikke riktig. Kostnad i mars, og utbetaling når lønna betales."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z16" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C17" s="22"/>
       <c r="G17" s="19" t="str">
         <f aca="false">IF(C17="","Velg i nedtrekksmenyen.",IF(C17="Begge","Riktig. Kostnad i mars i resultatbudsjettet, utbetaling i april i likviditetsbudsjettet. Begge, men i ulik måned.","Ikke riktig. Kostnad i mars i resultatbudsjettet, utbetaling i april i likviditetsbudsjettet. Begge, men i ulik måned."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z17" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C18" s="22"/>
       <c r="G18" s="19" t="str">
         <f aca="false">IF(C18="","Velg i nedtrekksmenyen.",IF(C18="Bare likviditetsbudsjettet","Riktig. Innbetaling uten inntekt. Lånet er ikke tjent, det er lånt.","Ikke riktig. Innbetaling uten inntekt. Lånet er ikke tjent, det er lånt."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z18" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C19" s="22"/>
       <c r="G19" s="19" t="str">
         <f aca="false">IF(C19="","Velg i nedtrekksmenyen.",IF(C19="Begge","Riktig. Kostnad og utbetaling, som regel i samme måned.","Ikke riktig. Kostnad og utbetaling, som regel i samme måned."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
+      <c r="Z19" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z20" s="0" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
+      <c r="Z21" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
+      <c r="Z22" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="18" t="s">
@@ -2847,10 +3007,13 @@
         <f aca="false">IF(C23="","Skriv svaret i den gule cellen.",IF(C23=(450000/5),"Riktig.",IF(ABS(C23-(450000))&lt;=0,"Du har tatt hele kjøpesummen. Den fordeles over 5 år.",IF(ABS(C23-(450000*1.25/5))&lt;=0,"Merverdiavgiften hører ikke hjemme i resultatbudsjettet.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z23" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="18" t="s">
@@ -2860,10 +3023,13 @@
         <f aca="false">IF(C24="","Skriv svaret i den gule cellen.",IF(C24=(450000*1.25),"Riktig.",IF(ABS(C24-(450000))&lt;=0,"Kontoen betaler fakturaen med merverdiavgift: 450 000 × 1,25.",IF(ABS(C24-(450000/5))&lt;=0,"Det er avskrivningen. Her spørres det om pengene som går ut av kontoen den måneden bilen kjøpes.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z24" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="18" t="s">
@@ -2873,16 +3039,27 @@
         <f aca="false">IF(C25="","Skriv svaret i den gule cellen.",IF(C25=(7500000*0.12),"Riktig.",IF(ABS(C25-(7500000*0.143))&lt;=0,"14,3 % gjelder bare ansatte som fyller 60. Her er satsen 12 %.",IF(ABS(C25-(890000))&lt;=0,"Det er feriepengene fra 2026, som utbetales i juni 2027. Oppgaven spør om dem som tjenes opp i 2027.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
+      <c r="Z25" s="24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z26" s="0" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
+      <c r="Z27" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="20"/>
@@ -2891,6 +3068,9 @@
       <c r="E28" s="20"/>
       <c r="F28" s="20"/>
       <c r="G28" s="20"/>
+      <c r="Z28" s="24" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="20"/>
@@ -2899,6 +3079,9 @@
       <c r="E29" s="20"/>
       <c r="F29" s="20"/>
       <c r="G29" s="20"/>
+      <c r="Z29" s="24" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="20"/>
@@ -2907,6 +3090,9 @@
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
+      <c r="Z30" s="24" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="21" t="str">
@@ -3069,43 +3255,43 @@
   </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C10" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C11" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$4:$Z$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C12" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$7:$Z$9</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C13" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$10:$Z$12</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C14" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$13:$Z$15</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C15" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$16:$Z$18</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C16" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$19:$Z$21</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C17" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$22:$Z$24</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C18" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$25:$Z$27</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C19" type="list">
-      <formula1>"Bare resultatbudsjettet,Bare likviditetsbudsjettet,Begge"</formula1>
+      <formula1>$Z$28:$Z$30</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C32" type="list">
@@ -3128,7 +3314,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G61"/>
+  <dimension ref="B1:Z61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3136,17 +3322,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>108</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -3157,6 +3352,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -3170,7 +3368,7 @@
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3190,7 +3388,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3200,7 +3398,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -3210,7 +3408,7 @@
     </row>
     <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3220,21 +3418,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2400000</v>
@@ -3248,7 +3446,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>750000</v>
@@ -3258,9 +3456,9 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="24" t="n">
+        <v>122</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <f aca="false">C13+C14</f>
         <v>3150000</v>
       </c>
@@ -3269,7 +3467,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>2100000</v>
@@ -3283,7 +3481,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>0</v>
@@ -3297,7 +3495,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>625000</v>
@@ -3311,7 +3509,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>170000</v>
@@ -3325,7 +3523,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>0</v>
@@ -3339,7 +3537,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>156250</v>
@@ -3353,7 +3551,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>0</v>
@@ -3367,7 +3565,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>0</v>
@@ -3381,7 +3579,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>0</v>
@@ -3395,26 +3593,26 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="24" t="n">
+        <v>132</v>
+      </c>
+      <c r="C25" s="25" t="n">
         <f aca="false">SUM(C16:C24)</f>
         <v>3051250</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <f aca="false">SUM(D16:D24)</f>
         <v>2283425</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <f aca="false">SUM(E16:E24)</f>
         <v>2734375</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="24" t="n">
+        <v>133</v>
+      </c>
+      <c r="C26" s="25" t="n">
         <f aca="false">C15-C25</f>
         <v>98750</v>
       </c>
@@ -3423,7 +3621,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>982650</v>
@@ -3433,9 +3631,9 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C28" s="24" t="n">
+        <v>135</v>
+      </c>
+      <c r="C28" s="25" t="n">
         <f aca="false">C27+C26</f>
         <v>1081400</v>
       </c>
@@ -3454,7 +3652,7 @@
     </row>
     <row r="31" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -3464,12 +3662,12 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C34" s="15" t="str">
         <f aca="false">IF(D14="","Skriv svaret i cellen D14.",IF(D14=(2250000*2/3+2625000/3),"Riktig.",IF(D14=(1800000*2/3+2100000/3),"Du har fordelt salget uten merverdiavgift. Kunden betaler salget × 1,25.",IF(D14=(2625000),"Du har tatt hele februarsalget. Med 20 dager kommer en tredel av februar og to tredeler av januar.",IF(D14=(2250000),"Du har tatt hele januarsalget. To tredeler av det kom i februar, pluss en tredel av februarsalget.","Ikke riktig ennå. To tredeler av januarsalget med merverdiavgift pluss en tredel av februarsalget med merverdiavgift.")))))</f>
@@ -3482,7 +3680,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C35" s="15" t="str">
         <f aca="false">IF(E14="","Skriv svaret i cellen E14.",IF(E14=(2625000*2/3+2812500/3),"Riktig.",IF(E14=(2100000*2/3+2250000/3),"Du har fordelt salget uten merverdiavgift. Gang med 1,25 først.",IF(E14=(2812500),"Du har tatt hele marssalget. Bare en tredel kommer i mars; resten i april.","Ikke riktig ennå. To tredeler av februarsalget med merverdiavgift pluss en tredel av marssalget med merverdiavgift."))))</f>
@@ -3495,7 +3693,7 @@
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C36" s="15" t="str">
         <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(D13+D14),"Riktig.",IF(D15=(D14),"Du har glemt de gamle kundefordringene, 1 800 000 i februar.","Ikke riktig ennå. Kundefordringene fra 2026 pluss innbetalt fra årets salg.")))</f>
@@ -3508,7 +3706,7 @@
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C37" s="15" t="str">
         <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(E14),"Riktig.",IF(E15=(E14+1800000),"Det er ingen gamle kundefordringer igjen i mars. Alt kom i januar og februar.","Ikke riktig ennå. I mars er det bare årets salg som kommer inn.")))</f>
@@ -3521,7 +3719,7 @@
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C38" s="15" t="str">
         <f aca="false">IF(D26="","Skriv svaret i cellen D26.",IF(D26=(D15-D25),"Riktig.",IF(D26=(D25-D15),"Du har snudd fortegnet. Innbetalinger minus utbetalinger.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger.")))</f>
@@ -3534,7 +3732,7 @@
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C39" s="15" t="str">
         <f aca="false">IF(E26="","Skriv svaret i cellen E26.",IF(E26=(E15-E25),"Riktig.",IF(E26=(E25-E15),"Du har snudd fortegnet. I mars går det mer ut enn inn, så tallet skal være negativt.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger. Negativt tall når mer går ut enn inn.")))</f>
@@ -3547,7 +3745,7 @@
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C40" s="15" t="str">
         <f aca="false">IF(D27="","Skriv svaret i cellen D27.",IF(D27=(C28),"Riktig.",IF(D27=(982650),"Det er beholdningen 1. januar. Februar starter med det januar sluttet med.","Ikke riktig ennå. Beholdningen ved starten av februar er beholdningen ved slutten av januar.")))</f>
@@ -3560,7 +3758,7 @@
     </row>
     <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C41" s="15" t="str">
         <f aca="false">IF(D28="","Skriv svaret i cellen D28.",IF(D28=(D27+D26),"Riktig.",IF(D28=(D27-D26),"Overskuddet skal legges til beholdningen, ikke trekkes fra.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet.")))</f>
@@ -3573,7 +3771,7 @@
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="C42" s="15" t="str">
         <f aca="false">IF(E27="","Skriv svaret i cellen E27.",IF(E27=(D28),"Riktig.","Ikke riktig ennå. Mars starter med det februar sluttet med."))</f>
@@ -3586,7 +3784,7 @@
     </row>
     <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C43" s="15" t="str">
         <f aca="false">IF(E28="","Skriv svaret i cellen E28.",IF(E28=(E27+E26),"Riktig.",IF(E28=(E27-E26),"Overskuddet i mars er negativt og skal legges til med fortegn: beholdningen går ned.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet (som er negativt i mars).")))</f>
@@ -3599,7 +3797,7 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="7" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
@@ -3609,7 +3807,7 @@
     </row>
     <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="8" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="C46" s="8"/>
       <c r="D46" s="8"/>
@@ -3619,7 +3817,7 @@
     </row>
     <row r="47" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="16" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C47" s="13"/>
       <c r="D47" s="18" t="s">
@@ -3632,7 +3830,7 @@
     </row>
     <row r="48" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="18" t="s">
@@ -3645,7 +3843,7 @@
     </row>
     <row r="49" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="18" t="s">
@@ -3658,7 +3856,7 @@
     </row>
     <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="16" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="C51" s="22"/>
       <c r="G51" s="19" t="str">
@@ -3668,7 +3866,7 @@
     </row>
     <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="8" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -3882,7 +4080,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="list">
-      <formula1>"Det blir lavere,fordi inntektene kommer senere,Det endres ikke med en krone,Det blir høyere,fordi kundene betaler renter"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C58" type="list">
@@ -3905,7 +4103,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G54"/>
+  <dimension ref="B1:Z54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3913,17 +4111,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -3934,6 +4141,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -3947,7 +4157,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3967,7 +4177,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3977,7 +4187,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -3987,7 +4197,7 @@
     </row>
     <row r="10" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3997,21 +4207,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>300000</v>
@@ -4025,7 +4235,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>500000</v>
@@ -4039,7 +4249,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>0</v>
@@ -4049,9 +4259,9 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="24" t="n">
+        <v>122</v>
+      </c>
+      <c r="C16" s="25" t="n">
         <f aca="false">SUM(C13:C15)</f>
         <v>800000</v>
       </c>
@@ -4060,7 +4270,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>375000</v>
@@ -4074,7 +4284,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>175000</v>
@@ -4088,7 +4298,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>150000</v>
@@ -4102,7 +4312,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>12000</v>
@@ -4116,7 +4326,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>10000</v>
@@ -4130,7 +4340,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>12000</v>
@@ -4144,7 +4354,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>17500</v>
@@ -4158,7 +4368,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>45000</v>
@@ -4172,7 +4382,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>0</v>
@@ -4186,24 +4396,24 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="24" t="n">
+        <v>132</v>
+      </c>
+      <c r="C26" s="25" t="n">
         <f aca="false">SUM(C17:C25)</f>
         <v>796500</v>
       </c>
-      <c r="D26" s="24" t="n">
+      <c r="D26" s="25" t="n">
         <f aca="false">SUM(D17:D25)</f>
         <v>351500</v>
       </c>
-      <c r="E26" s="24" t="n">
+      <c r="E26" s="25" t="n">
         <f aca="false">SUM(E17:E25)</f>
         <v>393800</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>0</v>
@@ -4213,7 +4423,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -4231,7 +4441,7 @@
     </row>
     <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4241,12 +4451,12 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="C34" s="15" t="str">
         <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(350000*1.25),"Riktig.",IF(D15=(350000),"Kunden betaler med merverdiavgift: 350 000 × 1,25.",IF(D15=(400000*1.25),"Du har tatt februarsalget. Med 30 dager kommer januarsalget i februar.","Ikke riktig ennå. Januarsalget med merverdiavgift: 350 000 × 1,25."))))</f>
@@ -4259,7 +4469,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C35" s="15" t="str">
         <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(400000*1.25),"Riktig.",IF(E15=(400000),"Gang med 1,25 for merverdiavgiften.",IF(E15=(350000*1.25),"Det er januarsalget, som kom i februar. I mars kommer februarsalget.","Ikke riktig ennå. Februarsalget med merverdiavgift: 400 000 × 1,25."))))</f>
@@ -4272,7 +4482,7 @@
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C36" s="15" t="str">
         <f aca="false">IF(D16="","Skriv svaret i cellen D16.",IF(D16=(D15),"Riktig.","Ikke riktig ennå. I februar er det bare kundene som betaler inn: 437 500."))</f>
@@ -4285,7 +4495,7 @@
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C37" s="15" t="str">
         <f aca="false">IF(E16="","Skriv svaret i cellen E16.",IF(E16=(E15),"Riktig.","Ikke riktig ennå. I mars er det bare kundene som betaler inn: 500 000."))</f>
@@ -4298,7 +4508,7 @@
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C38" s="15" t="str">
         <f aca="false">IF(D27="","Skriv svaret i cellen D27.",IF(D27=(C28),"Riktig.",IF(D27=(0),"Februar starter med det januar sluttet med, ikke med null.","Ikke riktig ennå. Saldo ved slutten av januar.")))</f>
@@ -4311,7 +4521,7 @@
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C39" s="15" t="str">
         <f aca="false">IF(E27="","Skriv svaret i cellen E27.",IF(E27=(D28),"Riktig.","Ikke riktig ennå. Saldo ved slutten av februar."))</f>
@@ -4324,7 +4534,7 @@
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C40" s="15" t="str">
         <f aca="false">IF(C28="","Skriv svaret i cellen C28.",IF(C28=(C27+C16-C26),"Riktig.",IF(C28=(C16-C26+350000*1.25),"Du har latt kundene betale i januar. Med 30 dagers kreditt kommer ingen kundepenger i januar.","Ikke riktig ennå. 0 + 800 000 − 796 500.")))</f>
@@ -4337,7 +4547,7 @@
     </row>
     <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C41" s="15" t="str">
         <f aca="false">IF(D28="","Skriv svaret i cellen D28.",IF(D28=(C28+D16-D26),"Riktig.",IF(D28=(D16-D26),"Du har glemt å starte med saldoen fra januar.","Ikke riktig ennå. Saldo ved start (slutten av januar) + inn − ut.")))</f>
@@ -4350,7 +4560,7 @@
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="C42" s="15" t="str">
         <f aca="false">IF(E28="","Skriv svaret i cellen E28.",IF(E28=(D28+E16-E26),"Riktig.",IF(E28=(E16-E26),"Start med saldoen fra februar.","Ikke riktig ennå. Saldo ved start (slutten av februar) + inn − ut.")))</f>
@@ -4363,7 +4573,7 @@
     </row>
     <row r="44" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="18" t="s">
@@ -4376,7 +4586,7 @@
     </row>
     <row r="45" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="16" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="18" t="s">
@@ -4389,7 +4599,7 @@
     </row>
     <row r="46" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="18" t="s">
@@ -4402,7 +4612,7 @@
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="C48" s="22"/>
       <c r="G48" s="19" t="str">
@@ -4412,7 +4622,7 @@
     </row>
     <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="18" t="s">
@@ -4588,7 +4798,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C48" type="list">
-      <formula1>"Fordi de er inntekter i oppstartsåret,Fordi likviditetsbudsjettet følger pengene,og resultatbudsjettet følger inntekter og kostnader,Fordi de er fradragsberettiget"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="list">
@@ -4611,7 +4821,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:G37"/>
+  <dimension ref="B1:Z37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4619,17 +4829,26 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="13"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Z1" s="0" t="s">
+        <v>189</v>
+      </c>
+    </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
+      <c r="Z2" s="24" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
@@ -4640,6 +4859,9 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
+      <c r="Z3" s="24" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="7" t="s">
@@ -4653,7 +4875,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -4673,7 +4895,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -4683,7 +4905,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -4693,7 +4915,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4706,10 +4928,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4725,7 +4947,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2306250</v>
@@ -4736,7 +4958,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>2752500</v>
@@ -4790,7 +5012,7 @@
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -4800,7 +5022,7 @@
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="18" t="s">
@@ -4813,7 +5035,7 @@
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="18" t="s">
@@ -4826,7 +5048,7 @@
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="18" t="s">
@@ -4839,7 +5061,7 @@
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18" t="s">
@@ -4852,7 +5074,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C27" s="22"/>
       <c r="G27" s="19" t="str">
@@ -4862,7 +5084,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="8" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -4992,7 +5214,7 @@
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C27" type="list">
-      <formula1>"Lønnskostnaden,som gikk opp 37 500,Varekostnaden: 96 000 av avviket forklares ikke av at salget økte,Avskrivningene"</formula1>
+      <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C34" type="list">
@@ -5025,528 +5247,528 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>194</v>
+      <c r="B2" s="26" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>198</v>
+      <c r="B5" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C6" s="24" t="n">
+      <c r="B6" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <v>9000000</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>200</v>
+      <c r="D6" s="28" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="24" t="n">
+      <c r="B7" s="28" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="25" t="n">
         <v>11010000</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>202</v>
+      <c r="D7" s="28" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="24" t="n">
+      <c r="B8" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="25" t="n">
         <v>720000</v>
       </c>
-      <c r="D8" s="27" t="s">
-        <v>204</v>
+      <c r="D8" s="28" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" s="24" t="n">
+      <c r="B9" s="28" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <v>1770000</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>206</v>
+      <c r="D9" s="28" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
-        <v>207</v>
-      </c>
-      <c r="C10" s="24" t="n">
+      <c r="B10" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <v>210000</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>208</v>
+      <c r="D10" s="28" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="24" t="n">
+      <c r="B11" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="25" t="n">
         <v>1616000</v>
       </c>
-      <c r="D11" s="27" t="s">
-        <v>210</v>
+      <c r="D11" s="28" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
-        <v>211</v>
-      </c>
-      <c r="C12" s="24" t="n">
+      <c r="B12" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="25" t="n">
         <v>7.4</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>212</v>
+      <c r="D12" s="28" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="24" t="n">
+      <c r="B13" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <v>1020000</v>
       </c>
-      <c r="D13" s="27" t="s">
-        <v>214</v>
+      <c r="D13" s="28" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
-        <v>215</v>
-      </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="27" t="s">
-        <v>216</v>
+      <c r="B14" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="28" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" s="24" t="n">
+      <c r="B15" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <v>4795000</v>
       </c>
-      <c r="D15" s="27" t="s">
-        <v>218</v>
+      <c r="D15" s="28" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
-        <v>219</v>
-      </c>
-      <c r="C16" s="24" t="n">
+      <c r="B16" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" s="25" t="n">
         <v>2671760</v>
       </c>
-      <c r="D16" s="27" t="s">
-        <v>220</v>
+      <c r="D16" s="28" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="27" t="s">
-        <v>221</v>
-      </c>
-      <c r="C17" s="24" t="n">
+      <c r="B17" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" s="25" t="n">
         <v>60000</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>222</v>
+      <c r="D17" s="28" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="s">
-        <v>223</v>
-      </c>
-      <c r="C18" s="24" t="n">
+      <c r="B18" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="25" t="n">
         <v>519000</v>
       </c>
-      <c r="D18" s="27" t="s">
-        <v>224</v>
+      <c r="D18" s="28" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
-        <v>225</v>
-      </c>
-      <c r="C19" s="24" t="n">
+      <c r="B19" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="25" t="n">
         <v>144240</v>
       </c>
-      <c r="D19" s="27" t="s">
-        <v>226</v>
+      <c r="D19" s="28" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
-        <v>227</v>
-      </c>
-      <c r="C20" s="24" t="n">
+      <c r="B20" s="28" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" s="25" t="n">
         <v>106740</v>
       </c>
-      <c r="D20" s="27" t="s">
-        <v>228</v>
+      <c r="D20" s="28" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="27" t="s">
-        <v>230</v>
+      <c r="B21" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="28" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="C22" s="24"/>
-      <c r="D22" s="27" t="s">
-        <v>232</v>
+      <c r="B22" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="28" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C23" s="24"/>
-      <c r="D23" s="27" t="s">
-        <v>234</v>
+      <c r="B23" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="28" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="24" t="n">
+      <c r="B24" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="25" t="n">
         <v>90000</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>236</v>
+      <c r="D24" s="28" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="24" t="n">
+      <c r="B25" s="28" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="25" t="n">
         <v>562500</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>238</v>
+      <c r="D25" s="28" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="C26" s="24" t="n">
+      <c r="B26" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" s="25" t="n">
         <v>900000</v>
       </c>
-      <c r="D26" s="27" t="s">
-        <v>240</v>
+      <c r="D26" s="28" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="C27" s="24"/>
-      <c r="D27" s="27" t="s">
-        <v>242</v>
+      <c r="B27" s="28" t="s">
+        <v>255</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="28" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" s="24" t="n">
+      <c r="B28" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="C28" s="25" t="n">
         <v>2375000</v>
       </c>
-      <c r="D28" s="27" t="s">
-        <v>244</v>
+      <c r="D28" s="28" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="C29" s="24" t="n">
+      <c r="B29" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="25" t="n">
         <v>2687500</v>
       </c>
-      <c r="D29" s="27" t="s">
-        <v>246</v>
+      <c r="D29" s="28" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="C30" s="24"/>
-      <c r="D30" s="27" t="s">
-        <v>248</v>
+      <c r="B30" s="28" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="28" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="27" t="s">
-        <v>250</v>
+      <c r="B31" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="28" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="C32" s="24" t="n">
+      <c r="B32" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="25" t="n">
         <v>2972975</v>
       </c>
-      <c r="D32" s="27" t="s">
-        <v>252</v>
+      <c r="D32" s="28" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="C33" s="24" t="n">
+      <c r="B33" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="C33" s="25" t="n">
         <v>2926100</v>
       </c>
-      <c r="D33" s="27" t="s">
-        <v>254</v>
+      <c r="D33" s="28" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C34" s="24" t="n">
+      <c r="B34" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C34" s="25" t="n">
         <v>-152025</v>
       </c>
-      <c r="D34" s="27" t="s">
-        <v>256</v>
+      <c r="D34" s="28" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C35" s="24" t="n">
+      <c r="B35" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="C35" s="25" t="n">
         <v>-636400</v>
       </c>
-      <c r="D35" s="27" t="s">
-        <v>258</v>
+      <c r="D35" s="28" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C36" s="24" t="n">
+      <c r="B36" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="C36" s="25" t="n">
         <v>636400</v>
       </c>
-      <c r="D36" s="27" t="s">
-        <v>260</v>
+      <c r="D36" s="28" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="27" t="s">
-        <v>262</v>
+      <c r="B37" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="28" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="27" t="s">
-        <v>264</v>
+      <c r="B38" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="28" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C39" s="24"/>
-      <c r="D39" s="27" t="s">
-        <v>266</v>
+      <c r="B39" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="28" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="C40" s="24" t="n">
+      <c r="B40" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" s="25" t="n">
         <v>3500</v>
       </c>
-      <c r="D40" s="27" t="s">
-        <v>268</v>
+      <c r="D40" s="28" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C41" s="24" t="n">
+      <c r="B41" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="C41" s="25" t="n">
         <v>89500</v>
       </c>
-      <c r="D41" s="27" t="s">
-        <v>270</v>
+      <c r="D41" s="28" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C42" s="24" t="n">
+      <c r="B42" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="C42" s="25" t="n">
         <v>195700</v>
       </c>
-      <c r="D42" s="27" t="s">
-        <v>272</v>
+      <c r="D42" s="28" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="C43" s="24" t="n">
+      <c r="B43" s="28" t="s">
+        <v>287</v>
+      </c>
+      <c r="C43" s="25" t="n">
         <v>-496500</v>
       </c>
-      <c r="D43" s="27" t="s">
-        <v>274</v>
+      <c r="D43" s="28" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="24" t="n">
+      <c r="B44" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="C44" s="25" t="n">
         <v>-348000</v>
       </c>
-      <c r="D44" s="27" t="s">
-        <v>276</v>
+      <c r="D44" s="28" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="C45" s="24" t="n">
+      <c r="B45" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C45" s="25" t="n">
         <v>-304300</v>
       </c>
-      <c r="D45" s="27" t="s">
-        <v>278</v>
+      <c r="D45" s="28" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="C46" s="24"/>
-      <c r="D46" s="27" t="s">
-        <v>280</v>
+      <c r="B46" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="25"/>
+      <c r="D46" s="28" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="C47" s="24" t="n">
+      <c r="B47" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="C47" s="25" t="n">
         <v>47500</v>
       </c>
-      <c r="D47" s="27" t="s">
-        <v>282</v>
+      <c r="D47" s="28" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="C48" s="24" t="n">
+      <c r="B48" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C48" s="25" t="n">
         <v>250000</v>
       </c>
-      <c r="D48" s="27" t="s">
-        <v>284</v>
+      <c r="D48" s="28" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="27" t="s">
-        <v>285</v>
-      </c>
-      <c r="C49" s="24" t="n">
+      <c r="B49" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="C49" s="25" t="n">
         <v>-189750</v>
       </c>
-      <c r="D49" s="27" t="s">
-        <v>286</v>
+      <c r="D49" s="28" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="C50" s="24" t="n">
+      <c r="B50" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="C50" s="25" t="n">
         <v>-12250</v>
       </c>
-      <c r="D50" s="27" t="s">
-        <v>288</v>
+      <c r="D50" s="28" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="27" t="s">
-        <v>289</v>
-      </c>
-      <c r="C51" s="24" t="n">
+      <c r="B51" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C51" s="25" t="n">
         <v>39</v>
       </c>
-      <c r="D51" s="27" t="s">
-        <v>290</v>
+      <c r="D51" s="28" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="27" t="s">
-        <v>291</v>
-      </c>
-      <c r="C52" s="24"/>
-      <c r="D52" s="27" t="s">
-        <v>292</v>
+      <c r="B52" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="28" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="27" t="s">
-        <v>294</v>
+      <c r="B53" s="28" t="s">
+        <v>307</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="28" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="312">
   <si>
     <t xml:space="preserve">Budsjettering og budsjettkontroll: oppgaver til kapittel 9</t>
   </si>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">Oppgave 1A: Nordlys' resultatbudsjett for 2027, linje for linje</t>
   </si>
   <si>
-    <t xml:space="preserve">Alene, i par eller i gruppe, slik du vil.</t>
+    <t xml:space="preserve">Økt 1 av 3, resultatbudsjettet. Alene, i par eller i gruppe, slik du vil.</t>
   </si>
   <si>
     <t xml:space="preserve">Situasjonen</t>
@@ -366,10 +366,13 @@
     <t xml:space="preserve">Det endres ikke med en krone</t>
   </si>
   <si>
+    <t xml:space="preserve">Økt 2 av 3, likviditetsbudsjettet. Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Det blir høyere, fordi kundene betaler renter</t>
   </si>
   <si>
-    <t xml:space="preserve">Budsjettet for 2027 viser 1 770 000 kr i driftsresultat. Likevel ringer regnskapsføreren: 1. januar står det 982 650 kr på driftskontoen, Polarlys skal ha 2 100 000 for materiellet fra desember, og kundene skylder 4 200 000, men de betaler når de betaler. Kari vil se pengene måned for måned. Januar er regnet ferdig; du regner februar og mars, og så hva som skjer hvis kundene betaler senere.</t>
+    <t xml:space="preserve">Budsjettet for 2027 viser 1 770 000 kr i driftsresultat. Likevel ringer regnskapsføreren: 1. januar står det 982 650 kr på driftskontoen, Polarlys skal ha 2 100 000 for materiellet fra desember, Skatteetaten skal ha 500 000 i skattetrekk fra desemberlønnen, og kundene skylder 4 200 000, men de betaler når de betaler. Kari vil se pengene måned for måned. Januar er regnet ferdig; du regner februar og mars, og så hva som skjer hvis kundene betaler senere.</t>
   </si>
   <si>
     <t xml:space="preserve">Likviditetsbudsjett: innbetalinger og utbetalinger i den måneden pengene flytter seg, alle beløp med merverdiavgift. Kredittid 20 dager: en tredel av salget betales i salgsmåneden, to tredeler måneden etter (boka regner 30 dager per måned). Innbetalingsoverskudd = sum innbetalinger − sum utbetalinger. Beholdning ved slutt = beholdning ved start + innbetalingsoverskudd. Kassekreditt: en avtalt ramme banken lar bedriften trekke på, mot rente.</t>
@@ -378,7 +381,7 @@
     <t xml:space="preserve">Forutsetningene</t>
   </si>
   <si>
-    <t xml:space="preserve">Salg uten merverdiavgift: januar 1 800 000, februar 2 100 000, mars 2 250 000 (fra salgsbudsjettet). Kundene betaler med 25 % merverdiavgift, altså salget × 1,25, og har 20 dagers kredittid: en tredel kommer inn i salgsmåneden, to tredeler måneden etter. Kundefordringene fra 2026, 4 200 000 kr, kommer inn med 2 400 000 i januar og 1 800 000 i februar. Utbetalingene står ferdig i tabellen: leverandørgjelden fra 2026 betales i januar; materiellet (37,5 % av salget, pluss merverdiavgift) betales måneden etter kjøpet; lønn 7 500 000 / 12 = 625 000 per måned; arbeidsgiveravgift for november–desember 2026 (170 000) forfaller 15. januar og for januar–februar (14,1 % × 2 × 625 000 = 176 250) 15. mars; merverdiavgift for november–desember 2026 (530 000) forfaller 10. februar; andre driftskostnader 1 500 000 / 12 × 1,25 = 156 250 per måned; renter og avdrag på banklånet kvartalsvis i mars (52 500 + 140 000); forhåndsskatt 15. februar er halve fjorårets skatt (256 850 / 2); termograferingsutstyret kjøpes i mars for 480 000 × 1,25. Beholdningen på driftskontoen 1. januar er 982 650 kr (balansen).</t>
+    <t xml:space="preserve">Salg uten merverdiavgift: januar 1 800 000, februar 2 100 000, mars 2 250 000 (fra salgsbudsjettet). Kundene betaler med 25 % merverdiavgift, altså salget × 1,25, og har 20 dagers kredittid: en tredel kommer inn i salgsmåneden, to tredeler måneden etter. Kundefordringene fra 2026, 4 200 000 kr, kommer inn med 2 400 000 i januar og 1 800 000 i februar. Utbetalingene står ferdig i tabellen: leverandørgjelden fra 2026 betales i januar; materiellet (37,5 % av salget, pluss merverdiavgift) betales måneden etter kjøpet; lønn 7 500 000 / 12 = 625 000 per måned; skattetrekket fra desemberlønnen, 500 000 kr i balansen, betales til Skatteetaten i januar; arbeidsgiveravgift for november–desember 2026 (170 000) forfaller 15. januar og for januar–februar (14,1 % × 2 × 625 000 = 176 250) 15. mars; merverdiavgift for november–desember 2026 (530 000) forfaller 10. februar; andre driftskostnader 1 500 000 / 12 × 1,25 = 156 250 per måned; renter og avdrag på banklånet kvartalsvis i mars (52 500 + 140 000); forhåndsskatt 15. februar er halve fjorårets skatt (256 850 / 2); termograferingsutstyret kjøpes i mars for 480 000 × 1,25. Beholdningen på driftskontoen 1. januar er 982 650 kr (balansen).</t>
   </si>
   <si>
     <t xml:space="preserve">Kroner</t>
@@ -409,6 +412,9 @@
   </si>
   <si>
     <t xml:space="preserve">Lønn og skattetrekk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skattetrekk fra desember 2026 (til Skatteetaten)</t>
   </si>
   <si>
     <t xml:space="preserve">Arbeidsgiveravgift (termin)</t>
@@ -491,7 +497,7 @@
     <t xml:space="preserve">b) Beholdning ved slutten av mars ved 60 dagers kredittid</t>
   </si>
   <si>
-    <t xml:space="preserve">c) Hvor mye må Nordlys trekke på kassekreditten i tillegg til de 300 000 for å dekke minus på kontoen 31. mars? (Hele kroner, positivt tall)</t>
+    <t xml:space="preserve">c) Hvor mye må Nordlys trekke på kassekreditten i tillegg til de 300 000 for å dekke minus på kontoen 31. mars? (Hele kroner, positivt tall.) Holder rammen?</t>
   </si>
   <si>
     <t xml:space="preserve">d) Kundene bruker 60 dager i stedet for 20. Hva skjer med driftsresultatet i resultatbudsjettet for 2027?</t>
@@ -518,7 +524,7 @@
     <t xml:space="preserve">I oppstarten går pengene ut før de kommer inn. Aksjekapital og lån er innbetalinger i likviditetsbudsjettet, aldri inntekter. Alle beløp er med merverdiavgift. Arbeidsgiveravgift og merverdiavgift betales terminvis: avgiften for januar–februar forfaller 15. mars, merverdiavgiften 10. april. Skyldig merverdiavgift = utgående (25 % av salget) − inngående (avgift betalt på kjøp).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS starter 1. januar med tom konto. Aksjekapitalen på 300 000 og banklånet på 500 000 kommer inn i januar. Salg uten merverdiavgift: januar 350 000, februar 400 000, mars 400 000; kundene betaler salget × 1,25 etter 30 dager, så januarsalget kommer i februar. Grossisten gir ikke kreditt det første halvåret, så materiellet betales i kjøpsmåneden, med merverdiavgift. Lønn er forenklet til 150 000 per måned (1 820 000 / 12 er 151 667). Pensjonspremien, 8 % av lønna, betales hver måned. Arbeidsgiveravgiften for januar–februar, 14,1 % × 300 000 = 42 300, forfaller 15. mars. Lokaler, leasing, forsikring og de andre postene er oppgitt som beløpet som går ut av kontoen. Merverdiavgift for januar–februar forfaller 10. april; forenklet regner vi inngående avgift bare på utstyr og materiell.</t>
+    <t xml:space="preserve">Fjell Elektro AS starter 1. januar med tom konto. Aksjekapitalen på 300 000 og banklånet på 500 000 kommer inn i januar. Salg uten merverdiavgift: januar 350 000, februar 400 000, mars 400 000; kundene betaler salget × 1,25 etter 30 dager, så januarsalget kommer i februar. Grossisten gir 30 dagers kreditt fra start, så materiellet betales måneden etter kjøpet, med merverdiavgift: januarkjøpet på 175 000 i februar og februarkjøpet på 150 000 i mars. Lønn er forenklet til 150 000 per måned (1 820 000 / 12 er 151 667). Pensjonspremien, 8 % av lønna, betales hver måned. Arbeidsgiveravgiften for januar–februar, 14,1 % × 300 000 = 42 300, forfaller 15. mars. Lokaler, leasing, forsikring og de andre postene er oppgitt som beløpet som går ut av kontoen. Merverdiavgift for januar–februar forfaller 10. april; forenklet regner vi inngående avgift bare på utstyr og materiell.</t>
   </si>
   <si>
     <t xml:space="preserve">Innbetalt aksjekapital</t>
@@ -533,7 +539,7 @@
     <t xml:space="preserve">Utstyr og verktøy (300 000 + merverdiavgift)</t>
   </si>
   <si>
-    <t xml:space="preserve">Materiell (med merverdiavgift, betalt i kjøpsmåneden)</t>
+    <t xml:space="preserve">Materiell (med merverdiavgift, betalt måneden etter)</t>
   </si>
   <si>
     <t xml:space="preserve">Lønn og skattetrekk (forenklet 150 000)</t>
@@ -613,10 +619,13 @@
     <t xml:space="preserve">Varekostnaden: 96 000 av avviket forklares ikke av at salget økte</t>
   </si>
   <si>
+    <t xml:space="preserve">Økt 3 av 3, budsjettkontroll og avvik. Alene, i par eller i gruppe, slik du vil.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Avskrivningene</t>
   </si>
   <si>
-    <t xml:space="preserve">Første kvartal er over. Kari setter regnskapet ved siden av budsjettet for kvartalet. Salget ble bedre enn planlagt, men driftsresultatet ble dårligere. Hun skal møte Ida (kalkulatør og innkjøp) på mandag og vil vite hva hun skal spørre om. Regn avvikene med riktig fortegn, så andelen av salget, og finn stedet Kari skal lete.</t>
+    <t xml:space="preserve">Første kvartal er over. Kari setter regnskapet ved siden av budsjettet for kvartalet. Salget ble bedre enn planlagt, men driftsresultatet ble dårligere. Hun skal møte Ida (kalkulatør) på mandag og vil vite hva hun skal spørre om. Regn avvikene med riktig fortegn, så andelen av salget, og finn stedet Kari skal lete.</t>
   </si>
   <si>
     <t xml:space="preserve">Budsjettkontroll: regnskapet sammenliknes med budsjettet for samme periode. Avvik for en inntekt = regnskap − budsjett; for en kostnad = budsjett − regnskap. Pluss er bra for resultatet, minus er dårlig. Avvik i prosent = avvik / budsjett × 100. Mengdeavvik: den delen av et kostnadsavvik som bare følger av at salget ble større; resten er prisavvik (pris, svinn, feil kalkyle).</t>
@@ -660,7 +669,7 @@
     <t xml:space="preserve">e) Hvor skal Kari lete først? Regn hver kostnad som andel av salget før du svarer.</t>
   </si>
   <si>
-    <t xml:space="preserve">f) Hva skal Kari spørre Ida (kalkulatør og innkjøp) om på mandag? To setninger: én om materiellet, én om andre driftskostnader. Spørsmålet skal peke på stedet, ikke på personen.</t>
+    <t xml:space="preserve">f) Hva skal Kari spørre Ida (kalkulatør) om på mandag? To setninger: én om materiellet, én om andre driftskostnader. Spørsmålet skal peke på stedet, ikke på personen.</t>
   </si>
   <si>
     <t xml:space="preserve">Fasit, kapittel 9</t>
@@ -837,31 +846,31 @@
     <t xml:space="preserve">2A Beholdning ved månedsslutt februar</t>
   </si>
   <si>
-    <t xml:space="preserve">1 081 400 + 1 891 575 = 2 972 975 kr</t>
+    <t xml:space="preserve">581 400 + 1 891 575 = 2 472 975 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2A Beholdning ved månedsslutt mars</t>
   </si>
   <si>
-    <t xml:space="preserve">2 972 975 − 46 875 = 2 926 100 kr</t>
+    <t xml:space="preserve">2 472 975 − 46 875 = 2 426 100 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2A a) Februar ved 60 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">Januar 982 650 + 2 400 000 − 3 051 250 = 331 400. Februar 331 400 + 1 800 000 − 2 283 425 = −152 025 kr</t>
+    <t xml:space="preserve">Januar 982 650 + 2 400 000 − 3 551 250 = −168 600. Februar −168 600 + 1 800 000 − 2 283 425 = −652 025 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2A b) Mars ved 60 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">−152 025 + 2 250 000 − 2 734 375 = −636 400 kr</t>
+    <t xml:space="preserve">−652 025 + 2 250 000 − 2 734 375 = −1 136 400 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2A c) Trekk på kassekreditten</t>
   </si>
   <si>
-    <t xml:space="preserve">636 400 kr i tillegg til 300 000: 936 400 av rammen på 1 000 000</t>
+    <t xml:space="preserve">1 136 400 kr i tillegg til 300 000: 1 436 400, som er 436 400 over rammen på 1 000 000. Rammen holder ikke</t>
   </si>
   <si>
     <t xml:space="preserve">2A d) Driftsresultatet</t>
@@ -885,37 +894,37 @@
     <t xml:space="preserve">2B Saldo 31. januar</t>
   </si>
   <si>
-    <t xml:space="preserve">0 + 800 000 − 796 500 = 3 500 kr</t>
+    <t xml:space="preserve">0 + 800 000 − 621 500 = 178 500 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B Saldo 28. februar</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 + 437 500 − 351 500 = 89 500 kr</t>
+    <t xml:space="preserve">178 500 + 437 500 − 376 500 = 239 500 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B Saldo 31. mars</t>
   </si>
   <si>
-    <t xml:space="preserve">89 500 + 500 000 − 393 800 = 195 700 kr</t>
+    <t xml:space="preserve">239 500 + 500 000 − 393 800 = 345 700 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B a) Uten banklånet</t>
   </si>
   <si>
-    <t xml:space="preserve">300 000 − 796 500 = −496 500 kr</t>
+    <t xml:space="preserve">300 000 − 621 500 = −321 500 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B b) Februar ved 60 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 − 351 500 = −348 000 kr</t>
+    <t xml:space="preserve">178 500 − 376 500 = −198 000 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B c) Mars ved 60 dager</t>
   </si>
   <si>
-    <t xml:space="preserve">−348 000 + 437 500 − 393 800 = −304 300 kr</t>
+    <t xml:space="preserve">−198 000 + 437 500 − 393 800 = −154 300 kr</t>
   </si>
   <si>
     <t xml:space="preserve">2B d) Aksjekapital og lån</t>
@@ -3314,7 +3323,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:Z61"/>
+  <dimension ref="B1:Z62"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -3345,7 +3354,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -3353,7 +3362,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="Z3" s="24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3368,7 +3377,7 @@
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3388,7 +3397,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3398,7 +3407,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -3408,7 +3417,7 @@
     </row>
     <row r="10" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3418,21 +3427,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2400000</v>
@@ -3446,7 +3455,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>750000</v>
@@ -3456,7 +3465,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="25" t="n">
         <f aca="false">C13+C14</f>
@@ -3467,7 +3476,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>2100000</v>
@@ -3481,7 +3490,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>0</v>
@@ -3495,7 +3504,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="12" t="n">
         <v>625000</v>
@@ -3509,182 +3518,183 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>170000</v>
+        <v>500000</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>176250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="12" t="n">
+        <v>170000</v>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="12" t="n">
-        <v>530000</v>
-      </c>
       <c r="E20" s="12" t="n">
-        <v>0</v>
+        <v>176250</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C21" s="12" t="n">
-        <v>156250</v>
+        <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>156250</v>
+        <v>530000</v>
       </c>
       <c r="E21" s="12" t="n">
-        <v>156250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>0</v>
+        <v>156250</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0</v>
+        <v>156250</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>192500</v>
+        <v>156250</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>128425</v>
+        <v>0</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0</v>
+        <v>192500</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="12" t="n">
+        <v>128425</v>
+      </c>
+      <c r="E24" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>600000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="25" t="n">
-        <f aca="false">SUM(C16:C24)</f>
-        <v>3051250</v>
-      </c>
-      <c r="D25" s="25" t="n">
-        <f aca="false">SUM(D16:D24)</f>
-        <v>2283425</v>
-      </c>
-      <c r="E25" s="25" t="n">
-        <f aca="false">SUM(E16:E24)</f>
-        <v>2734375</v>
+        <v>133</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>600000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="25" t="n">
-        <f aca="false">C15-C25</f>
-        <v>98750</v>
-      </c>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+        <f aca="false">SUM(C16:C25)</f>
+        <v>3551250</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <f aca="false">SUM(D16:D25)</f>
+        <v>2283425</v>
+      </c>
+      <c r="E26" s="25" t="n">
+        <f aca="false">SUM(E16:E25)</f>
+        <v>2734375</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="12" t="n">
-        <v>982650</v>
+        <v>135</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <f aca="false">C15-C26</f>
+        <v>-401250</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="25" t="n">
-        <f aca="false">C27+C26</f>
-        <v>1081400</v>
+        <v>136</v>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>982650</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="7" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <f aca="false">C28+C27</f>
+        <v>581400</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="15" t="str">
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="C35" s="15" t="str">
         <f aca="false">IF(D14="","Skriv svaret i cellen D14.",IF(D14=(2250000*2/3+2625000/3),"Riktig.",IF(D14=(1800000*2/3+2100000/3),"Du har fordelt salget uten merverdiavgift. Kunden betaler salget × 1,25.",IF(D14=(2625000),"Du har tatt hele februarsalget. Med 20 dager kommer en tredel av februar og to tredeler av januar.",IF(D14=(2250000),"Du har tatt hele januarsalget. To tredeler av det kom i februar, pluss en tredel av februarsalget.","Ikke riktig ennå. To tredeler av januarsalget med merverdiavgift pluss en tredel av februarsalget med merverdiavgift.")))))</f>
         <v>Skriv svaret i cellen D14.</v>
-      </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="C35" s="15" t="str">
-        <f aca="false">IF(E14="","Skriv svaret i cellen E14.",IF(E14=(2625000*2/3+2812500/3),"Riktig.",IF(E14=(2100000*2/3+2250000/3),"Du har fordelt salget uten merverdiavgift. Gang med 1,25 først.",IF(E14=(2812500),"Du har tatt hele marssalget. Bare en tredel kommer i mars; resten i april.","Ikke riktig ennå. To tredeler av februarsalget med merverdiavgift pluss en tredel av marssalget med merverdiavgift."))))</f>
-        <v>Skriv svaret i cellen E14.</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="15"/>
@@ -3693,11 +3703,11 @@
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C36" s="15" t="str">
-        <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(D13+D14),"Riktig.",IF(D15=(D14),"Du har glemt de gamle kundefordringene, 1 800 000 i februar.","Ikke riktig ennå. Kundefordringene fra 2026 pluss innbetalt fra årets salg.")))</f>
-        <v>Skriv svaret i cellen D15.</v>
+        <f aca="false">IF(E14="","Skriv svaret i cellen E14.",IF(E14=(2625000*2/3+2812500/3),"Riktig.",IF(E14=(2100000*2/3+2250000/3),"Du har fordelt salget uten merverdiavgift. Gang med 1,25 først.",IF(E14=(2812500),"Du har tatt hele marssalget. Bare en tredel kommer i mars; resten i april.","Ikke riktig ennå. To tredeler av februarsalget med merverdiavgift pluss en tredel av marssalget med merverdiavgift."))))</f>
+        <v>Skriv svaret i cellen E14.</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="15"/>
@@ -3706,11 +3716,11 @@
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C37" s="15" t="str">
-        <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(E14),"Riktig.",IF(E15=(E14+1800000),"Det er ingen gamle kundefordringer igjen i mars. Alt kom i januar og februar.","Ikke riktig ennå. I mars er det bare årets salg som kommer inn.")))</f>
-        <v>Skriv svaret i cellen E15.</v>
+        <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(D13+D14),"Riktig.",IF(D15=(D14),"Du har glemt de gamle kundefordringene, 1 800 000 i februar.","Ikke riktig ennå. Kundefordringene fra 2026 pluss innbetalt fra årets salg.")))</f>
+        <v>Skriv svaret i cellen D15.</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="15"/>
@@ -3719,11 +3729,11 @@
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C38" s="15" t="str">
-        <f aca="false">IF(D26="","Skriv svaret i cellen D26.",IF(D26=(D15-D25),"Riktig.",IF(D26=(D25-D15),"Du har snudd fortegnet. Innbetalinger minus utbetalinger.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger.")))</f>
-        <v>Skriv svaret i cellen D26.</v>
+        <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(E14),"Riktig.",IF(E15=(E14+1800000),"Det er ingen gamle kundefordringer igjen i mars. Alt kom i januar og februar.","Ikke riktig ennå. I mars er det bare årets salg som kommer inn.")))</f>
+        <v>Skriv svaret i cellen E15.</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
@@ -3732,11 +3742,11 @@
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" s="15" t="str">
-        <f aca="false">IF(E26="","Skriv svaret i cellen E26.",IF(E26=(E15-E25),"Riktig.",IF(E26=(E25-E15),"Du har snudd fortegnet. I mars går det mer ut enn inn, så tallet skal være negativt.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger. Negativt tall når mer går ut enn inn.")))</f>
-        <v>Skriv svaret i cellen E26.</v>
+        <f aca="false">IF(D27="","Skriv svaret i cellen D27.",IF(D27=(D15-D26),"Riktig.",IF(D27=(D26-D15),"Du har snudd fortegnet. Innbetalinger minus utbetalinger.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger.")))</f>
+        <v>Skriv svaret i cellen D27.</v>
       </c>
       <c r="D39" s="15"/>
       <c r="E39" s="15"/>
@@ -3745,11 +3755,11 @@
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C40" s="15" t="str">
-        <f aca="false">IF(D27="","Skriv svaret i cellen D27.",IF(D27=(C28),"Riktig.",IF(D27=(982650),"Det er beholdningen 1. januar. Februar starter med det januar sluttet med.","Ikke riktig ennå. Beholdningen ved starten av februar er beholdningen ved slutten av januar.")))</f>
-        <v>Skriv svaret i cellen D27.</v>
+        <f aca="false">IF(E27="","Skriv svaret i cellen E27.",IF(E27=(E15-E26),"Riktig.",IF(E27=(E26-E15),"Du har snudd fortegnet. I mars går det mer ut enn inn, så tallet skal være negativt.","Ikke riktig ennå. Sum innbetalinger minus sum utbetalinger. Negativt tall når mer går ut enn inn.")))</f>
+        <v>Skriv svaret i cellen E27.</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="15"/>
@@ -3758,10 +3768,10 @@
     </row>
     <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C41" s="15" t="str">
-        <f aca="false">IF(D28="","Skriv svaret i cellen D28.",IF(D28=(D27+D26),"Riktig.",IF(D28=(D27-D26),"Overskuddet skal legges til beholdningen, ikke trekkes fra.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet.")))</f>
+        <f aca="false">IF(D28="","Skriv svaret i cellen D28.",IF(D28=(C29),"Riktig.",IF(D28=(982650),"Det er beholdningen 1. januar. Februar starter med det januar sluttet med.","Ikke riktig ennå. Beholdningen ved starten av februar er beholdningen ved slutten av januar.")))</f>
         <v>Skriv svaret i cellen D28.</v>
       </c>
       <c r="D41" s="15"/>
@@ -3771,11 +3781,11 @@
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C42" s="15" t="str">
-        <f aca="false">IF(E27="","Skriv svaret i cellen E27.",IF(E27=(D28),"Riktig.","Ikke riktig ennå. Mars starter med det februar sluttet med."))</f>
-        <v>Skriv svaret i cellen E27.</v>
+        <f aca="false">IF(D29="","Skriv svaret i cellen D29.",IF(D29=(D28+D27),"Riktig.",IF(D29=(D28-D27),"Overskuddet skal legges til beholdningen, ikke trekkes fra.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet.")))</f>
+        <v>Skriv svaret i cellen D29.</v>
       </c>
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
@@ -3784,10 +3794,10 @@
     </row>
     <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C43" s="15" t="str">
-        <f aca="false">IF(E28="","Skriv svaret i cellen E28.",IF(E28=(E27+E26),"Riktig.",IF(E28=(E27-E26),"Overskuddet i mars er negativt og skal legges til med fortegn: beholdningen går ned.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet (som er negativt i mars).")))</f>
+        <f aca="false">IF(E28="","Skriv svaret i cellen E28.",IF(E28=(D29),"Riktig.","Ikke riktig ennå. Mars starter med det februar sluttet med."))</f>
         <v>Skriv svaret i cellen E28.</v>
       </c>
       <c r="D43" s="15"/>
@@ -3795,92 +3805,97 @@
       <c r="F43" s="15"/>
       <c r="G43" s="15"/>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-    </row>
-    <row r="46" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="8" t="s">
+    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-    </row>
-    <row r="47" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="16" t="s">
+      <c r="C44" s="15" t="str">
+        <f aca="false">IF(E29="","Skriv svaret i cellen E29.",IF(E29=(E28+E27),"Riktig.",IF(E29=(E28-E27),"Overskuddet i mars er negativt og skal legges til med fortegn: beholdningen går ned.","Ikke riktig ennå. Beholdning ved start pluss innbetalingsoverskuddet (som er negativt i mars).")))</f>
+        <v>Skriv svaret i cellen E29.</v>
+      </c>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="G47" s="19" t="str">
-        <f aca="false">IF(C47="","Skriv svaret i den gule cellen.",IF(C47=(982650+2400000-3051250+1800000-2283425),"Riktig.",IF(ABS(C47-(982650+2400000-3051250+1800000+2250000-2283425))&lt;=0,"Du har latt januarsalget komme i februar. Med 60 dager kommer det først i mars.",IF(ABS(C47-(982650+2400000+750000-3051250+1800000+2375000-2283425))&lt;=0,"Det er budsjettet med 20 dager. Nå skal alt salg komme to måneder etter.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
-        <v>Skriv svaret i den gule cellen.</v>
-      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8"/>
     </row>
     <row r="48" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G48" s="19" t="str">
-        <f aca="false">IF(C48="","Skriv svaret i den gule cellen.",IF(C48=(982650+2400000-3051250+1800000-2283425+2250000-2734375),"Riktig.",IF(ABS(C48-(982650+2400000-3051250+1800000-2283425-2734375))&lt;=0,"Du har glemt januarsalget, 2 250 000 med merverdiavgift, som kommer inn i mars.",IF(ABS(C48-(982650+2400000-3051250+1800000-2283425+2625000-2734375))&lt;=0,"Du har tatt februarsalget. I mars kommer januarsalget (to måneder etter).","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C48="","Skriv svaret i den gule cellen.",IF(C48=(982650+2400000-3551250+1800000-2283425),"Riktig.",IF(ABS(C48-(982650+2400000-3551250+1800000+2250000-2283425))&lt;=0,"Du har latt januarsalget komme i februar. Med 60 dager kommer det først i mars.",IF(ABS(C48-(982650+2400000+750000-3551250+1800000+2375000-2283425))&lt;=0,"Det er budsjettet med 20 dager. Nå skal alt salg komme to måneder etter.",IF(ABS(C48-(982650+2400000-3051250+1800000-2283425))&lt;=0,"Du har glemt skattetrekket fra desember, 500 000, som betales i januar.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G49" s="19" t="str">
-        <f aca="false">IF(C49="","Skriv svaret i den gule cellen.",IF(C49=(-(982650+2400000-3051250+1800000-2283425+2250000-2734375)),"Riktig.",IF(ABS(C49-(1000000))&lt;=0,"Rammen er 1 000 000, men spørsmålet er hvor mye som må trekkes: beløpet kontoen er i minus.",IF(ABS(C49-(-(982650+2400000-3051250+1800000-2283425+2250000-2734375)+300000))&lt;=0,"De 300 000 var trukket fra før. Spørsmålet er tillegget: det kontoen er i minus 31. mars.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
+        <f aca="false">IF(C49="","Skriv svaret i den gule cellen.",IF(C49=(982650+2400000-3551250+1800000-2283425+2250000-2734375),"Riktig.",IF(ABS(C49-(982650+2400000-3551250+1800000-2283425-2734375))&lt;=0,"Du har glemt januarsalget, 2 250 000 med merverdiavgift, som kommer inn i mars.",IF(ABS(C49-(982650+2400000-3551250+1800000-2283425+2625000-2734375))&lt;=0,"Du har tatt februarsalget. I mars kommer januarsalget (to måneder etter).","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="C51" s="22"/>
-      <c r="G51" s="19" t="str">
-        <f aca="false">IF(C51="","Velg i nedtrekksmenyen.",IF(C51="Det endres ikke med en krone","Riktig. Inntekten føres når fakturaen skrives, ikke når den betales. Kredittiden endrer bare likviditetsbudsjettet: driftsresultatet er 1 770 000 i begge tilfeller.","Ikke riktig. Inntekten føres når fakturaen skrives, ikke når den betales. Kredittiden endrer bare likviditetsbudsjettet: driftsresultatet er 1 770 000 i begge tilfeller."))</f>
+    <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="13"/>
+      <c r="D50" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="19" t="str">
+        <f aca="false">IF(C50="","Skriv svaret i den gule cellen.",IF(C50=(-(982650+2400000-3551250+1800000-2283425+2250000-2734375)),"Riktig.",IF(ABS(C50-(1000000))&lt;=0,"Rammen er 1 000 000, men spørsmålet er hvor mye som må trekkes: beløpet kontoen er i minus.",IF(ABS(C50-(-(982650+2400000-3551250+1800000-2283425+2250000-2734375)+300000))&lt;=0,"De 300 000 var trukket fra før. Spørsmålet er tillegget: det kontoen er i minus 31. mars.",IF(ABS(C50-(1000000-300000))&lt;=0,"Det er det som er igjen av rammen. Spørsmålet er hvor mye som trengs: det kontoen er i minus 31. mars.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))))</f>
+        <v>Skriv svaret i den gule cellen.</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="G52" s="19" t="str">
+        <f aca="false">IF(C52="","Velg i nedtrekksmenyen.",IF(C52="Det endres ikke med en krone","Riktig. Inntekten føres når fakturaen skrives, ikke når den betales. Kredittiden endrer bare likviditetsbudsjettet: driftsresultatet er 1 770 000 i begge tilfeller.","Ikke riktig. Inntekten føres når fakturaen skrives, ikke når den betales. Kredittiden endrer bare likviditetsbudsjettet: driftsresultatet er 1 770 000 i begge tilfeller."))</f>
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-    </row>
-    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="20"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
+    <row r="54" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="20"/>
@@ -3898,43 +3913,51 @@
       <c r="F56" s="20"/>
       <c r="G56" s="20"/>
     </row>
-    <row r="57" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="21" t="str">
-        <f aca="false">IF(LEN(B54)&lt;40,"",IF(AND(ISNUMBER(SEARCH("faktur",B54)),ISNUMBER(SEARCH("kassekreditt",B54))),"Bra: du starter med det som er gratis og treffer årsaken (fakturering og kredittid), og du sier hvorfor kassekreditten kommer sist: den koster rente og løser ikke problemet.",IF(OR(ISNUMBER(SEARCH("faktur",B54)),ISNUMBER(SEARCH("kassekreditt",B54))),"Du er på sporet. Nevn et konkret tiltak overfor kundene først, og si at kassekreditten bare gir lov til å ligge i minus, mot rente.","Tips: fakturer samme dag som jobben er ferdig, bruk e-faktura, purr tidlig, krev forskudd på store jobber, og be Polarlys om lengre kredittid. Kassekreditten endrer ingenting i budsjettet; den koster 7,5 % rente og problemet er like stort neste år.")))</f>
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+    </row>
+    <row r="58" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="21" t="str">
+        <f aca="false">IF(LEN(B55)&lt;40,"",IF(AND(ISNUMBER(SEARCH("faktur",B55)),ISNUMBER(SEARCH("kassekreditt",B55))),"Bra: du starter med det som er gratis og treffer årsaken (fakturering og kredittid), og du sier hvorfor kassekreditten kommer sist: den koster rente og løser ikke problemet.",IF(OR(ISNUMBER(SEARCH("faktur",B55)),ISNUMBER(SEARCH("kassekreditt",B55))),"Du er på sporet. Nevn et konkret tiltak overfor kundene først, og si at kassekreditten bare gir lov til å ligge i minus, mot rente.","Tips: fakturer samme dag som jobben er ferdig, bruk e-faktura, purr tidlig, krev forskudd på store jobber, og be Polarlys om lengre kredittid. Kassekreditten endrer ingenting i budsjettet; den koster 7,5 % rente og problemet er like stort neste år.")))</f>
         <v/>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="14" t="s">
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C58" s="22"/>
-    </row>
-    <row r="59" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="23" t="str">
-        <f aca="false">IF(C58="JA","Hint: Februar: innbetalt 2 250 000 × 2/3 + 2 625 000 / 3 = 2 375 000, pluss 1 800 000 gamle fordringer = 4 175 000. Ut 2 283 425. Overskudd 1 891 575. Beholdning 1 081 400 + 1 891 575 = 2 972 975. Mars: innbetalt 2 625 000 × 2/3 + 2 812 500 / 3 = 2 687 500. Ut 2 734 375. Overskudd −46 875. Beholdning 2 926 100. Ved 60 dager: januar 982 650 + 2 400 000 − 3 051 250 = 331 400; februar 331 400 + 1 800 000 − 2 283 425 = −152 025; mars −152 025 + 2 250 000 − 2 734 375 = −636 400.","")</f>
+      <c r="C59" s="22"/>
+    </row>
+    <row r="60" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="23" t="str">
+        <f aca="false">IF(C59="JA","Hint: Januar: ut 3 551 250 med skattetrekket fra desember; beholdning 982 650 + 3 150 000 − 3 551 250 = 581 400. Februar: innbetalt 2 250 000 × 2/3 + 2 625 000 / 3 = 2 375 000, pluss 1 800 000 gamle fordringer = 4 175 000. Ut 2 283 425. Overskudd 1 891 575. Beholdning 581 400 + 1 891 575 = 2 472 975. Mars: innbetalt 2 625 000 × 2/3 + 2 812 500 / 3 = 2 687 500. Ut 2 734 375. Overskudd −46 875. Beholdning 2 426 100. Ved 60 dager: januar 982 650 + 2 400 000 − 3 551 250 = −168 600; februar −168 600 + 1 800 000 − 2 283 425 = −652 025; mars −652 025 + 2 250 000 − 2 734 375 = −1 136 400.","")</f>
         <v/>
       </c>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-    </row>
-    <row r="61" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="6" t="s">
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="23"/>
+    </row>
+    <row r="62" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -3946,9 +3969,8 @@
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B9:G9"/>
     <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B30:G30"/>
     <mergeCell ref="B31:G31"/>
-    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="B32:G32"/>
     <mergeCell ref="C35:G35"/>
     <mergeCell ref="C36:G36"/>
     <mergeCell ref="C37:G37"/>
@@ -3958,132 +3980,133 @@
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="C42:G42"/>
     <mergeCell ref="C43:G43"/>
-    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C44:G44"/>
     <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G56"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="B47:G47"/>
+    <mergeCell ref="B54:G54"/>
+    <mergeCell ref="B55:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B62:G62"/>
   </mergeCells>
-  <conditionalFormatting sqref="C34">
+  <conditionalFormatting sqref="C35">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C34,6)="Riktig"</formula>
+      <formula>LEFT(C35,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C34&lt;&gt;"",LEFT(C34,6)&lt;&gt;"Riktig",LEFT(C34,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
+      <formula>AND(C35&lt;&gt;"",LEFT(C35,6)&lt;&gt;"Riktig",LEFT(C35,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36">
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C35,6)="Riktig"</formula>
+      <formula>LEFT(C36,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C35&lt;&gt;"",LEFT(C35,6)&lt;&gt;"Riktig",LEFT(C35,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C36">
+      <formula>AND(C36&lt;&gt;"",LEFT(C36,6)&lt;&gt;"Riktig",LEFT(C36,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C37">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C36,6)="Riktig"</formula>
+      <formula>LEFT(C37,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C36&lt;&gt;"",LEFT(C36,6)&lt;&gt;"Riktig",LEFT(C36,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C37">
+      <formula>AND(C37&lt;&gt;"",LEFT(C37,6)&lt;&gt;"Riktig",LEFT(C37,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C38">
     <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C37,6)="Riktig"</formula>
+      <formula>LEFT(C38,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C37&lt;&gt;"",LEFT(C37,6)&lt;&gt;"Riktig",LEFT(C37,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C38">
+      <formula>AND(C38&lt;&gt;"",LEFT(C38,6)&lt;&gt;"Riktig",LEFT(C38,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
     <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C38,6)="Riktig"</formula>
+      <formula>LEFT(C39,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C38&lt;&gt;"",LEFT(C38,6)&lt;&gt;"Riktig",LEFT(C38,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C39">
+      <formula>AND(C39&lt;&gt;"",LEFT(C39,6)&lt;&gt;"Riktig",LEFT(C39,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C40">
     <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C39,6)="Riktig"</formula>
+      <formula>LEFT(C40,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C39&lt;&gt;"",LEFT(C39,6)&lt;&gt;"Riktig",LEFT(C39,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C40">
+      <formula>AND(C40&lt;&gt;"",LEFT(C40,6)&lt;&gt;"Riktig",LEFT(C40,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41">
     <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C40,6)="Riktig"</formula>
+      <formula>LEFT(C41,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C40&lt;&gt;"",LEFT(C40,6)&lt;&gt;"Riktig",LEFT(C40,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41">
+      <formula>AND(C41&lt;&gt;"",LEFT(C41,6)&lt;&gt;"Riktig",LEFT(C41,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C42">
     <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C41,6)="Riktig"</formula>
+      <formula>LEFT(C42,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C41&lt;&gt;"",LEFT(C41,6)&lt;&gt;"Riktig",LEFT(C41,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C42">
+      <formula>AND(C42&lt;&gt;"",LEFT(C42,6)&lt;&gt;"Riktig",LEFT(C42,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C43">
     <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C42,6)="Riktig"</formula>
+      <formula>LEFT(C43,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C42&lt;&gt;"",LEFT(C42,6)&lt;&gt;"Riktig",LEFT(C42,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C43">
+      <formula>AND(C43&lt;&gt;"",LEFT(C43,6)&lt;&gt;"Riktig",LEFT(C43,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C44">
     <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(C43,6)="Riktig"</formula>
+      <formula>LEFT(C44,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(C43&lt;&gt;"",LEFT(C43,6)&lt;&gt;"Riktig",LEFT(C43,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G47">
+      <formula>AND(C44&lt;&gt;"",LEFT(C44,6)&lt;&gt;"Riktig",LEFT(C44,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G48">
     <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G47,6)="Riktig"</formula>
+      <formula>LEFT(G48,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(G47&lt;&gt;"",LEFT(G47,6)&lt;&gt;"Riktig",LEFT(G47,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G48">
+      <formula>AND(G48&lt;&gt;"",LEFT(G48,6)&lt;&gt;"Riktig",LEFT(G48,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G49">
     <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G48,6)="Riktig"</formula>
+      <formula>LEFT(G49,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(G48&lt;&gt;"",LEFT(G48,6)&lt;&gt;"Riktig",LEFT(G48,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G49">
+      <formula>AND(G49&lt;&gt;"",LEFT(G49,6)&lt;&gt;"Riktig",LEFT(G49,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G50">
     <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G49,6)="Riktig"</formula>
+      <formula>LEFT(G50,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND(G49&lt;&gt;"",LEFT(G49,6)&lt;&gt;"Riktig",LEFT(G49,5)&lt;&gt;"Skriv")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G51">
+      <formula>AND(G50&lt;&gt;"",LEFT(G50,6)&lt;&gt;"Riktig",LEFT(G50,5)&lt;&gt;"Skriv")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G52">
     <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>LEFT(G51,6)="Riktig"</formula>
+      <formula>LEFT(G52,6)="Riktig"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>LEFT(G51,4)="Ikke"</formula>
+      <formula>LEFT(G52,4)="Ikke"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C51" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C52" type="list">
       <formula1>$Z$1:$Z$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C58" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C59" type="list">
       <formula1>"JA,NEI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -4116,12 +4139,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z1" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -4129,12 +4152,12 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="Z2" s="24" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -4142,7 +4165,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="Z3" s="24" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4157,7 +4180,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -4177,7 +4200,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -4187,7 +4210,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -4195,9 +4218,9 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4207,21 +4230,21 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>300000</v>
@@ -4235,7 +4258,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>500000</v>
@@ -4249,7 +4272,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C15" s="12" t="n">
         <v>0</v>
@@ -4259,7 +4282,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="25" t="n">
         <f aca="false">SUM(C13:C15)</f>
@@ -4270,7 +4293,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>375000</v>
@@ -4284,13 +4307,13 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>175000</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>150000</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>150000</v>
@@ -4298,7 +4321,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>150000</v>
@@ -4312,7 +4335,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>12000</v>
@@ -4326,7 +4349,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C21" s="12" t="n">
         <v>10000</v>
@@ -4340,7 +4363,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>12000</v>
@@ -4354,7 +4377,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C23" s="12" t="n">
         <v>17500</v>
@@ -4368,7 +4391,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C24" s="12" t="n">
         <v>45000</v>
@@ -4382,7 +4405,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>0</v>
@@ -4396,15 +4419,15 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C26" s="25" t="n">
         <f aca="false">SUM(C17:C25)</f>
-        <v>796500</v>
+        <v>621500</v>
       </c>
       <c r="D26" s="25" t="n">
         <f aca="false">SUM(D17:D25)</f>
-        <v>351500</v>
+        <v>376500</v>
       </c>
       <c r="E26" s="25" t="n">
         <f aca="false">SUM(E17:E25)</f>
@@ -4413,7 +4436,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>0</v>
@@ -4423,7 +4446,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
@@ -4441,7 +4464,7 @@
     </row>
     <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -4451,12 +4474,12 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C34" s="15" t="str">
         <f aca="false">IF(D15="","Skriv svaret i cellen D15.",IF(D15=(350000*1.25),"Riktig.",IF(D15=(350000),"Kunden betaler med merverdiavgift: 350 000 × 1,25.",IF(D15=(400000*1.25),"Du har tatt februarsalget. Med 30 dager kommer januarsalget i februar.","Ikke riktig ennå. Januarsalget med merverdiavgift: 350 000 × 1,25."))))</f>
@@ -4469,7 +4492,7 @@
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C35" s="15" t="str">
         <f aca="false">IF(E15="","Skriv svaret i cellen E15.",IF(E15=(400000*1.25),"Riktig.",IF(E15=(400000),"Gang med 1,25 for merverdiavgiften.",IF(E15=(350000*1.25),"Det er januarsalget, som kom i februar. I mars kommer februarsalget.","Ikke riktig ennå. Februarsalget med merverdiavgift: 400 000 × 1,25."))))</f>
@@ -4482,7 +4505,7 @@
     </row>
     <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C36" s="15" t="str">
         <f aca="false">IF(D16="","Skriv svaret i cellen D16.",IF(D16=(D15),"Riktig.","Ikke riktig ennå. I februar er det bare kundene som betaler inn: 437 500."))</f>
@@ -4495,7 +4518,7 @@
     </row>
     <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C37" s="15" t="str">
         <f aca="false">IF(E16="","Skriv svaret i cellen E16.",IF(E16=(E15),"Riktig.","Ikke riktig ennå. I mars er det bare kundene som betaler inn: 500 000."))</f>
@@ -4508,7 +4531,7 @@
     </row>
     <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C38" s="15" t="str">
         <f aca="false">IF(D27="","Skriv svaret i cellen D27.",IF(D27=(C28),"Riktig.",IF(D27=(0),"Februar starter med det januar sluttet med, ikke med null.","Ikke riktig ennå. Saldo ved slutten av januar.")))</f>
@@ -4521,7 +4544,7 @@
     </row>
     <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C39" s="15" t="str">
         <f aca="false">IF(E27="","Skriv svaret i cellen E27.",IF(E27=(D28),"Riktig.","Ikke riktig ennå. Saldo ved slutten av februar."))</f>
@@ -4534,10 +4557,10 @@
     </row>
     <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C40" s="15" t="str">
-        <f aca="false">IF(C28="","Skriv svaret i cellen C28.",IF(C28=(C27+C16-C26),"Riktig.",IF(C28=(C16-C26+350000*1.25),"Du har latt kundene betale i januar. Med 30 dagers kreditt kommer ingen kundepenger i januar.","Ikke riktig ennå. 0 + 800 000 − 796 500.")))</f>
+        <f aca="false">IF(C28="","Skriv svaret i cellen C28.",IF(C28=(C27+C16-C26),"Riktig.",IF(C28=(C16-C26+350000*1.25),"Du har latt kundene betale i januar. Med 30 dagers kreditt kommer ingen kundepenger i januar.","Ikke riktig ennå. 0 + 800 000 − 621 500.")))</f>
         <v>Skriv svaret i cellen C28.</v>
       </c>
       <c r="D40" s="15"/>
@@ -4547,7 +4570,7 @@
     </row>
     <row r="41" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C41" s="15" t="str">
         <f aca="false">IF(D28="","Skriv svaret i cellen D28.",IF(D28=(C28+D16-D26),"Riktig.",IF(D28=(D16-D26),"Du har glemt å starte med saldoen fra januar.","Ikke riktig ennå. Saldo ved start (slutten av januar) + inn − ut.")))</f>
@@ -4560,7 +4583,7 @@
     </row>
     <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="0" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C42" s="15" t="str">
         <f aca="false">IF(E28="","Skriv svaret i cellen E28.",IF(E28=(D28+E16-E26),"Riktig.",IF(E28=(E16-E26),"Start med saldoen fra februar.","Ikke riktig ennå. Saldo ved start (slutten av februar) + inn − ut.")))</f>
@@ -4573,46 +4596,46 @@
     </row>
     <row r="44" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C44" s="13"/>
       <c r="D44" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G44" s="19" t="str">
-        <f aca="false">IF(C44="","Skriv svaret i den gule cellen.",IF(C44=(300000-796500),"Riktig.",IF(ABS(C44-(300000-796500+500000))&lt;=0,"Det er saldoen med lånet. Oppgaven spør hva som skjer uten de 500 000.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C44="","Skriv svaret i den gule cellen.",IF(C44=(300000-621500),"Riktig.",IF(ABS(C44-(300000-621500+500000))&lt;=0,"Det er saldoen med lånet. Oppgaven spør hva som skjer uten de 500 000.",IF(ABS(C44-(300000-796500))&lt;=0,"Du har betalt januarmateriellet i januar. Med 30 dagers kreditt betales det i februar.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene."))))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C45" s="13"/>
       <c r="D45" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G45" s="19" t="str">
-        <f aca="false">IF(C45="","Skriv svaret i den gule cellen.",IF(C45=(800000-796500-351500),"Riktig.",IF(ABS(C45-(800000-796500+437500-351500))&lt;=0,"Det er saldoen med 30 dager. Med 60 dager kommer ingen kundepenger i februar.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C45="","Skriv svaret i den gule cellen.",IF(C45=(800000-621500-376500),"Riktig.",IF(ABS(C45-(800000-621500+437500-376500))&lt;=0,"Det er saldoen med 30 dager. Med 60 dager kommer ingen kundepenger i februar.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="18" t="s">
         <v>48</v>
       </c>
       <c r="G46" s="19" t="str">
-        <f aca="false">IF(C46="","Skriv svaret i den gule cellen.",IF(C46=(800000-796500-351500+437500-393800),"Riktig.",IF(ABS(C46-(800000-796500-351500+500000-393800))&lt;=0,"Du har latt februarsalget komme i mars. Med 60 dager er det januarsalget, 437 500.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
+        <f aca="false">IF(C46="","Skriv svaret i den gule cellen.",IF(C46=(800000-621500-376500+437500-393800),"Riktig.",IF(ABS(C46-(800000-621500-376500+500000-393800))&lt;=0,"Du har latt februarsalget komme i mars. Med 60 dager er det januarsalget, 437 500.","Ikke riktig ennå. Se på regnestykket øverst på fanen, og sjekk at du har med alle leddene.")))</f>
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C48" s="22"/>
       <c r="G48" s="19" t="str">
@@ -4622,7 +4645,7 @@
     </row>
     <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="18" t="s">
@@ -4641,7 +4664,7 @@
     </row>
     <row r="52" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="23" t="str">
-        <f aca="false">IF(C51="JA","Hint: Januar: inn 300 000 + 500 000 = 800 000, ut 796 500, saldo 3 500. Februar: 3 500 + 437 500 − 351 500 = 89 500. Mars: 89 500 + 500 000 − 393 800 = 195 700. Uten lån: 300 000 − 796 500 = −496 500. Ved 60 dager: februar 3 500 − 351 500 = −348 000; mars −348 000 + 437 500 − 393 800 = −304 300. Merverdiavgift: 187 500 − 140 000 = 47 500.","")</f>
+        <f aca="false">IF(C51="JA","Hint: Januar: inn 300 000 + 500 000 = 800 000, ut 621 500 (materiellet betales først i februar), saldo 178 500. Februar: 178 500 + 437 500 − 376 500 = 239 500. Mars: 239 500 + 500 000 − 393 800 = 345 700. Uten lån: 300 000 − 621 500 = −321 500. Ved 60 dager: februar 178 500 − 376 500 = −198 000; mars −198 000 + 437 500 − 393 800 = −154 300. Merverdiavgift: 187 500 − 140 000 = 47 500.","")</f>
         <v/>
       </c>
       <c r="C52" s="23"/>
@@ -4834,12 +4857,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="Z1" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -4847,12 +4870,12 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="Z2" s="24" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>17</v>
+        <v>194</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -4860,7 +4883,7 @@
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="Z3" s="24" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4875,7 +4898,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -4895,7 +4918,7 @@
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="8" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -4905,7 +4928,7 @@
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -4915,7 +4938,7 @@
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="8" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -4928,10 +4951,10 @@
         <v>24</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4947,7 +4970,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>2306250</v>
@@ -4958,7 +4981,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C14" s="12" t="n">
         <v>2752500</v>
@@ -5012,7 +5035,7 @@
     </row>
     <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -5022,7 +5045,7 @@
     </row>
     <row r="22" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="18" t="s">
@@ -5035,7 +5058,7 @@
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="18" t="s">
@@ -5048,7 +5071,7 @@
     </row>
     <row r="24" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="18" t="s">
@@ -5061,7 +5084,7 @@
     </row>
     <row r="25" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="16" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="18" t="s">
@@ -5074,7 +5097,7 @@
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C27" s="22"/>
       <c r="G27" s="19" t="str">
@@ -5084,7 +5107,7 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -5248,527 +5271,527 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="26" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="28" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>9000000</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="28" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>11010000</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="28" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>720000</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="28" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>1770000</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="28" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>210000</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>1616000</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="28" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C12" s="25" t="n">
         <v>7.4</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="28" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>1020000</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="28" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C14" s="25"/>
       <c r="D14" s="28" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C15" s="25" t="n">
         <v>4795000</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="28" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C16" s="25" t="n">
         <v>2671760</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="28" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C17" s="25" t="n">
         <v>60000</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="28" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C18" s="25" t="n">
         <v>519000</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="28" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C19" s="25" t="n">
         <v>144240</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="28" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C20" s="25" t="n">
         <v>106740</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="28" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="28" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="28" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C22" s="25"/>
       <c r="D22" s="28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="28" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C23" s="25"/>
       <c r="D23" s="28" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="28" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C24" s="25" t="n">
         <v>90000</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="28" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C25" s="25" t="n">
         <v>562500</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="28" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C26" s="25" t="n">
         <v>900000</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="28" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C27" s="25"/>
       <c r="D27" s="28" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="28" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C28" s="25" t="n">
         <v>2375000</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="28" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C29" s="25" t="n">
         <v>2687500</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="28" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C30" s="25"/>
       <c r="D30" s="28" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="28" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C31" s="25"/>
       <c r="D31" s="28" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="28" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>2972975</v>
+        <v>2472975</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="28" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>2926100</v>
+        <v>2426100</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="28" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>-152025</v>
+        <v>-652025</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="28" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>-636400</v>
+        <v>-1136400</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="28" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C36" s="25" t="n">
-        <v>636400</v>
+        <v>1136400</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="28" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C37" s="25"/>
       <c r="D37" s="28" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="28" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="28" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="28" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C39" s="25"/>
       <c r="D39" s="28" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="28" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C40" s="25" t="n">
-        <v>3500</v>
+        <v>178500</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="28" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>89500</v>
+        <v>239500</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="28" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C42" s="25" t="n">
-        <v>195700</v>
+        <v>345700</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="28" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C43" s="25" t="n">
-        <v>-496500</v>
+        <v>-321500</v>
       </c>
       <c r="D43" s="28" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="28" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C44" s="25" t="n">
-        <v>-348000</v>
+        <v>-198000</v>
       </c>
       <c r="D44" s="28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C45" s="25" t="n">
-        <v>-304300</v>
+        <v>-154300</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="28" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C46" s="25"/>
       <c r="D46" s="28" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C47" s="25" t="n">
         <v>47500</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="28" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C48" s="25" t="n">
         <v>250000</v>
       </c>
       <c r="D48" s="28" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="28" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C49" s="25" t="n">
         <v>-189750</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="28" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C50" s="25" t="n">
         <v>-12250</v>
       </c>
       <c r="D50" s="28" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="28" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C51" s="25" t="n">
         <v>39</v>
       </c>
       <c r="D51" s="28" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="28" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="28" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="28" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="28" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
+++ b/pensum/ok09/OK09_Budsjettering_Oppgaver_v6.xlsx
@@ -1151,7 +1151,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1266,6 +1266,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1553,7 +1557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
@@ -1578,42 +1582,42 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
@@ -1943,7 +1947,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="16" t="s">
         <v>47</v>
       </c>
@@ -1956,7 +1960,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="8" t="s">
         <v>49</v>
       </c>
@@ -2312,8 +2316,8 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
+    <row ht="46.5" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B17" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="12" t="n">
@@ -2336,8 +2340,8 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B20" t="s">
         <v>70</v>
       </c>
       <c r="C20" s="12" t="n">
@@ -2354,7 +2358,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="8" t="s">
         <v>71</v>
       </c>
@@ -2416,7 +2420,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="16" t="s">
         <v>76</v>
       </c>
@@ -2830,7 +2834,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="17.25" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
         <v>91</v>
       </c>
@@ -3488,8 +3492,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B17" t="s">
         <v>125</v>
       </c>
       <c r="C17" s="12" t="n">
@@ -3864,7 +3868,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
         <v>154</v>
       </c>
@@ -3877,7 +3881,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="52" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="16" t="s">
         <v>155</v>
       </c>
@@ -4375,8 +4379,8 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
+    <row ht="31.5" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="29" r="B23" t="s">
         <v>173</v>
       </c>
       <c r="C23" s="12" t="n">
@@ -4462,7 +4466,7 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="31" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="8" t="s">
         <v>178</v>
       </c>
@@ -4594,7 +4598,7 @@
       <c r="F42" s="15"/>
       <c r="G42" s="15"/>
     </row>
-    <row r="44" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="44" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="16" t="s">
         <v>186</v>
       </c>
@@ -4607,7 +4611,7 @@
         <v>Skriv svaret i den gule cellen.</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="45" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="16" t="s">
         <v>187</v>
       </c>
@@ -4643,7 +4647,7 @@
         <v>Velg i nedtrekksmenyen.</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="46.5" customHeight="true" r="50" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="16" t="s">
         <v>190</v>
       </c>
@@ -5033,7 +5037,7 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="60.75" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
         <v>204</v>
       </c>
